--- a/backtest_runs/20260410_193731/by_symbol/IML/IML.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/IML/IML.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-3095.500000000001</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>96904.5</v>
@@ -1047,7 +1047,7 @@
         <v>-1208.000000000001</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>125368</v>
@@ -1185,7 +1185,7 @@
         <v>-9022.249999999989</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>120120.75</v>
@@ -1231,7 +1231,7 @@
         <v>-6228.750000000008</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>113892</v>
@@ -1369,7 +1369,7 @@
         <v>-5549.249999999995</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>115968.25</v>
@@ -1415,7 +1415,7 @@
         <v>-226.4999999999952</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>115741.75</v>
@@ -1553,7 +1553,7 @@
         <v>-2302.750000000011</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>125368</v>
